--- a/AtchisonRegime/Outputs/India/MSCI_Europe/df_regTrendSummaryMSCI_Europe.xlsx
+++ b/AtchisonRegime/Outputs/India/MSCI_Europe/df_regTrendSummaryMSCI_Europe.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1066,35 +1066,13 @@
         <v>45291</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>45596</v>
+        <v>45777</v>
       </c>
       <c r="E29" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F29" t="n">
-        <v>0.126916639387032</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Type 3</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>45626</v>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>45747</v>
-      </c>
-      <c r="E30" t="n">
-        <v>5</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.1412669016474817</v>
+        <v>0.3096731848285368</v>
       </c>
     </row>
   </sheetData>
